--- a/docs/data/jp/xlsx/9932.xlsx
+++ b/docs/data/jp/xlsx/9932.xlsx
@@ -7304,7 +7304,7 @@
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>Purchase Discounts NOI</t>
+          <t>매입할인</t>
         </is>
       </c>
       <c r="C97" s="20" t="n">
@@ -11468,7 +11468,7 @@
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>Purchase Of Goodwill Inv CF</t>
+          <t>영업권 취득 지출</t>
         </is>
       </c>
       <c r="Q178" s="20" t="n">
@@ -11484,7 +11484,7 @@
     <row r="179">
       <c r="A179" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Liquidation Of Subsidiaries And Affiliates Inv CF</t>
+          <t>관계회사 정리 수입</t>
         </is>
       </c>
       <c r="E179" s="20" t="n">
@@ -16418,7 +16418,7 @@
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>Long Term Guarantee Deposited</t>
+          <t>장기 예수보증금</t>
         </is>
       </c>
       <c r="C126" s="20" t="n">
